--- a/etf_holdings/2026-08-26_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:03</t>
+          <t>2026-08-26 16:02:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:03</t>
+          <t>2026-08-26 16:02:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:03</t>
+          <t>2026-08-26 16:02:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:03</t>
+          <t>2026-08-26 16:02:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:03</t>
+          <t>2026-08-26 16:02:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:03</t>
+          <t>2026-08-26 16:02:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:03</t>
+          <t>2026-08-26 16:02:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:03</t>
+          <t>2026-08-26 16:02:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:03</t>
+          <t>2026-08-26 16:02:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:03</t>
+          <t>2026-08-26 16:02:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:03</t>
+          <t>2026-08-26 16:02:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:03</t>
+          <t>2026-08-26 16:02:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:03</t>
+          <t>2026-08-26 16:02:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:03</t>
+          <t>2026-08-26 16:02:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:03</t>
+          <t>2026-08-26 16:02:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:04</t>
+          <t>2026-08-26 16:02:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:04</t>
+          <t>2026-08-26 16:02:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:04</t>
+          <t>2026-08-26 16:02:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:04</t>
+          <t>2026-08-26 16:02:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:04</t>
+          <t>2026-08-26 16:02:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:04</t>
+          <t>2026-08-26 16:02:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:04</t>
+          <t>2026-08-26 16:02:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:04</t>
+          <t>2026-08-26 16:02:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:04</t>
+          <t>2026-08-26 16:02:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:04</t>
+          <t>2026-08-26 16:02:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:04</t>
+          <t>2026-08-26 16:02:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:04</t>
+          <t>2026-08-26 16:02:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:04</t>
+          <t>2026-08-26 16:02:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:04</t>
+          <t>2026-08-26 16:02:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:04</t>
+          <t>2026-08-26 16:02:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:05</t>
+          <t>2026-08-26 16:02:04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:05</t>
+          <t>2026-08-26 16:02:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:05</t>
+          <t>2026-08-26 16:02:04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:05</t>
+          <t>2026-08-26 16:02:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:05</t>
+          <t>2026-08-26 16:02:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:05</t>
+          <t>2026-08-26 16:02:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:05</t>
+          <t>2026-08-26 16:02:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:05</t>
+          <t>2026-08-26 16:02:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:05</t>
+          <t>2026-08-26 16:02:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:05</t>
+          <t>2026-08-26 16:02:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 15:57:05</t>
+          <t>2026-08-26 16:02:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-26_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:02</t>
+          <t>2026-08-26 19:35:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.77%260,000</t>
+          <t>8.65%260,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.77%</t>
+          <t>8.65%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:02</t>
+          <t>2026-08-26 19:35:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.63%2415</t>
+          <t>+6.95%3155</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+6.95%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2415</v>
+        <v>3155</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.40%1,306,000</t>
+          <t>7.25%1,001,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.40%</t>
+          <t>7.25%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1306000</v>
+        <v>1001000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:02</t>
+          <t>2026-08-26 19:35:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+6.95%3155</t>
+          <t>+0.63%2415</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+6.95%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3155</v>
+        <v>2415</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.97%1,001,000</t>
+          <t>7.24%1,306,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>7.24%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1001000</v>
+        <v>1306000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:02</t>
+          <t>2026-08-26 19:35:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.42%2,482,000</t>
+          <t>6.61%2,482,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.42%</t>
+          <t>6.61%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:02</t>
+          <t>2026-08-26 19:35:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.14%465,000</t>
+          <t>6.29%465,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.14%</t>
+          <t>6.29%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:02</t>
+          <t>2026-08-26 19:35:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.69%1,161,000</t>
+          <t>5.34%1,161,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>5.34%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:02</t>
+          <t>2026-08-26 19:35:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.15%1,074,000</t>
+          <t>5.06%1,074,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.15%</t>
+          <t>5.06%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:02</t>
+          <t>2026-08-26 19:35:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-1.65%1195</t>
+          <t>+9.97%6290</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>+9.97%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1195</v>
+        <v>6290</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.67%1,630,000</t>
+          <t>4.95%343,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.67%</t>
+          <t>4.95%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1630000</v>
+        <v>343000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:02</t>
+          <t>2026-08-26 19:35:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+9.97%6290</t>
+          <t>-1.65%1195</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+9.97%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6290</v>
+        <v>1195</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.63%343,000</t>
+          <t>4.47%1,630,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.63%</t>
+          <t>4.47%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>343000</v>
+        <v>1630000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:02</t>
+          <t>2026-08-26 19:35:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.54%268,000</t>
+          <t>3.10%268,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.10%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:02</t>
+          <t>2026-08-26 19:35:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.13%2,231,000</t>
+          <t>3.09%2,231,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:02</t>
+          <t>2026-08-26 19:35:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.05%7,245,000</t>
+          <t>3.02%7,245,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.02%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:02</t>
+          <t>2026-08-26 19:35:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.80%10,877,000</t>
+          <t>2.94%10,877,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:02</t>
+          <t>2026-08-26 19:35:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.73%2,753,000</t>
+          <t>2.70%2,753,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.70%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:02</t>
+          <t>2026-08-26 19:35:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+3.59%418.5</t>
+          <t>+9.81%207</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+3.59%</t>
+          <t>+9.81%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>418.5</v>
+        <v>207</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.56%2,682,000</t>
+          <t>2.59%5,445,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.59%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2682000</v>
+        <v>5445000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:03</t>
+          <t>2026-08-26 19:35:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+2.34%1750</t>
+          <t>+3.59%418.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+2.34%</t>
+          <t>+3.59%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1750</v>
+        <v>418.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.55%632,000</t>
+          <t>2.58%2,682,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>632000</v>
+        <v>2682000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:03</t>
+          <t>2026-08-26 19:35:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+9.81%207</t>
+          <t>+2.34%1750</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+9.81%</t>
+          <t>+2.34%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>207</v>
+        <v>1750</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.42%5,445,000</t>
+          <t>2.54%632,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.54%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>5445000</v>
+        <v>632000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:03</t>
+          <t>2026-08-26 19:35:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.35%266,000</t>
+          <t>2.41%266,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:03</t>
+          <t>2026-08-26 19:35:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.16%164,000</t>
+          <t>2.30%164,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:03</t>
+          <t>2026-08-26 19:35:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.96%215,000</t>
+          <t>1.95%215,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:03</t>
+          <t>2026-08-26 19:35:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.66%844,013</t>
+          <t>1.71%844,013</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:03</t>
+          <t>2026-08-26 19:35:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.17%77,000</t>
+          <t>1.20%77,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:03</t>
+          <t>2026-08-26 19:35:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.05%1,000,000</t>
+          <t>1.04%1,000,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:03</t>
+          <t>2026-08-26 19:35:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.00%716,000</t>
+          <t>0.97%716,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:03</t>
+          <t>2026-08-26 19:35:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.82%300,000</t>
+          <t>0.81%300,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:03</t>
+          <t>2026-08-26 19:35:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.47%373,000</t>
+          <t>0.50%373,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:03</t>
+          <t>2026-08-26 19:35:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+3.72%307</t>
+          <t>+9.97%3255</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+3.72%</t>
+          <t>+9.97%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>307</v>
+        <v>3255</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.46%659,000</t>
+          <t>0.47%63,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>659000</v>
+        <v>63000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:03</t>
+          <t>2026-08-26 19:35:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,34 +2151,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6139亞翔</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+4.17%800</t>
+          <t>+3.72%307</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+4.17%</t>
+          <t>+3.72%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>800</v>
+        <v>307</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.45%250,000</t>
+          <t>0.46%659,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>250000</v>
+        <v>659000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:03</t>
+          <t>2026-08-26 19:35:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>6139亞翔</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+9.97%3255</t>
+          <t>+4.17%800</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+9.97%</t>
+          <t>+4.17%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3255</v>
+        <v>800</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.44%63,000</t>
+          <t>0.46%250,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>63000</v>
+        <v>250000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:03</t>
+          <t>2026-08-26 19:35:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.43%196,000</t>
+          <t>0.44%196,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:04</t>
+          <t>2026-08-26 19:35:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.15%351.5</t>
+          <t>+9.99%5725</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.15%</t>
+          <t>+9.99%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>351.5</v>
+        <v>5725</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.42%508,000</t>
+          <t>0.43%33,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>508000</v>
+        <v>33000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:04</t>
+          <t>2026-08-26 19:35:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,25 +2395,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+9.99%5725</t>
+          <t>+1.15%351.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+9.99%</t>
+          <t>+1.15%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5725</v>
+        <v>351.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.41%33,000</t>
+          <t>0.41%508,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2422,11 +2422,11 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>33000</v>
+        <v>508000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:04</t>
+          <t>2026-08-26 19:35:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.40%1,957,000</t>
+          <t>0.41%1,957,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:04</t>
+          <t>2026-08-26 19:35:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:04</t>
+          <t>2026-08-26 19:35:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.88%15690</t>
+          <t>+3.03%1530</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.88%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>15690</v>
+        <v>1530</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.40%11,000</t>
+          <t>0.40%113,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>11000</v>
+        <v>113000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:04</t>
+          <t>2026-08-26 19:35:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+3.03%1530</t>
+          <t>+1.88%15690</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>+1.88%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1530</v>
+        <v>15690</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.40%113,000</t>
+          <t>0.40%11,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>113000</v>
+        <v>11000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:04</t>
+          <t>2026-08-26 19:35:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.39%155,000</t>
+          <t>0.38%155,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:04</t>
+          <t>2026-08-26 19:35:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.39%261,000</t>
+          <t>0.37%261,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:04</t>
+          <t>2026-08-26 19:35:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:04</t>
+          <t>2026-08-26 19:35:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.35%98,000</t>
+          <t>0.34%98,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 16:02:04</t>
+          <t>2026-08-26 19:35:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-26_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:29</t>
+          <t>2026-08-26 21:15:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:29</t>
+          <t>2026-08-26 21:15:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:29</t>
+          <t>2026-08-26 21:15:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:29</t>
+          <t>2026-08-26 21:15:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:29</t>
+          <t>2026-08-26 21:15:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:29</t>
+          <t>2026-08-26 21:15:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:29</t>
+          <t>2026-08-26 21:15:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:29</t>
+          <t>2026-08-26 21:15:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:29</t>
+          <t>2026-08-26 21:15:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:29</t>
+          <t>2026-08-26 21:15:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:29</t>
+          <t>2026-08-26 21:15:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:29</t>
+          <t>2026-08-26 21:15:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:29</t>
+          <t>2026-08-26 21:15:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:29</t>
+          <t>2026-08-26 21:15:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:29</t>
+          <t>2026-08-26 21:15:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:30</t>
+          <t>2026-08-26 21:15:29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:30</t>
+          <t>2026-08-26 21:15:29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:30</t>
+          <t>2026-08-26 21:15:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:30</t>
+          <t>2026-08-26 21:15:29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:30</t>
+          <t>2026-08-26 21:15:29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:30</t>
+          <t>2026-08-26 21:15:29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:30</t>
+          <t>2026-08-26 21:15:29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:30</t>
+          <t>2026-08-26 21:15:29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:30</t>
+          <t>2026-08-26 21:15:29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:30</t>
+          <t>2026-08-26 21:15:29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:30</t>
+          <t>2026-08-26 21:15:29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:30</t>
+          <t>2026-08-26 21:15:29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:30</t>
+          <t>2026-08-26 21:15:29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:30</t>
+          <t>2026-08-26 21:15:29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:30</t>
+          <t>2026-08-26 21:15:29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:31</t>
+          <t>2026-08-26 21:15:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:31</t>
+          <t>2026-08-26 21:15:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:31</t>
+          <t>2026-08-26 21:15:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:31</t>
+          <t>2026-08-26 21:15:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:31</t>
+          <t>2026-08-26 21:15:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:31</t>
+          <t>2026-08-26 21:15:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:31</t>
+          <t>2026-08-26 21:15:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:31</t>
+          <t>2026-08-26 21:15:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:31</t>
+          <t>2026-08-26 21:15:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:31</t>
+          <t>2026-08-26 21:15:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 19:35:31</t>
+          <t>2026-08-26 21:15:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-26_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:27</t>
+          <t>2026-08-26 21:38:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:27</t>
+          <t>2026-08-26 21:38:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:27</t>
+          <t>2026-08-26 21:38:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:27</t>
+          <t>2026-08-26 21:38:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:27</t>
+          <t>2026-08-26 21:38:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:27</t>
+          <t>2026-08-26 21:38:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:27</t>
+          <t>2026-08-26 21:38:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:27</t>
+          <t>2026-08-26 21:38:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:27</t>
+          <t>2026-08-26 21:38:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:27</t>
+          <t>2026-08-26 21:38:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:27</t>
+          <t>2026-08-26 21:38:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:27</t>
+          <t>2026-08-26 21:38:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:27</t>
+          <t>2026-08-26 21:38:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:27</t>
+          <t>2026-08-26 21:38:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:27</t>
+          <t>2026-08-26 21:38:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:29</t>
+          <t>2026-08-26 21:38:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:29</t>
+          <t>2026-08-26 21:38:49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:29</t>
+          <t>2026-08-26 21:38:49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:29</t>
+          <t>2026-08-26 21:38:49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:29</t>
+          <t>2026-08-26 21:38:49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:29</t>
+          <t>2026-08-26 21:38:49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:29</t>
+          <t>2026-08-26 21:38:49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:29</t>
+          <t>2026-08-26 21:38:49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:29</t>
+          <t>2026-08-26 21:38:49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:29</t>
+          <t>2026-08-26 21:38:49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:29</t>
+          <t>2026-08-26 21:38:49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:29</t>
+          <t>2026-08-26 21:38:49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:29</t>
+          <t>2026-08-26 21:38:49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:29</t>
+          <t>2026-08-26 21:38:49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:29</t>
+          <t>2026-08-26 21:38:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:30</t>
+          <t>2026-08-26 21:38:50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:30</t>
+          <t>2026-08-26 21:38:50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:30</t>
+          <t>2026-08-26 21:38:50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:30</t>
+          <t>2026-08-26 21:38:50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:30</t>
+          <t>2026-08-26 21:38:50</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:30</t>
+          <t>2026-08-26 21:38:50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:30</t>
+          <t>2026-08-26 21:38:50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:30</t>
+          <t>2026-08-26 21:38:50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:30</t>
+          <t>2026-08-26 21:38:50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:30</t>
+          <t>2026-08-26 21:38:50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 21:15:30</t>
+          <t>2026-08-26 21:38:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-26_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:46</t>
+          <t>2026-08-26 22:08:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:46</t>
+          <t>2026-08-26 22:08:01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:46</t>
+          <t>2026-08-26 22:08:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:46</t>
+          <t>2026-08-26 22:08:01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:46</t>
+          <t>2026-08-26 22:08:01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:46</t>
+          <t>2026-08-26 22:08:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:46</t>
+          <t>2026-08-26 22:08:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:46</t>
+          <t>2026-08-26 22:08:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:46</t>
+          <t>2026-08-26 22:08:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:46</t>
+          <t>2026-08-26 22:08:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:46</t>
+          <t>2026-08-26 22:08:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:46</t>
+          <t>2026-08-26 22:08:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:46</t>
+          <t>2026-08-26 22:08:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:46</t>
+          <t>2026-08-26 22:08:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:46</t>
+          <t>2026-08-26 22:08:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:49</t>
+          <t>2026-08-26 22:08:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:49</t>
+          <t>2026-08-26 22:08:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:49</t>
+          <t>2026-08-26 22:08:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:49</t>
+          <t>2026-08-26 22:08:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:49</t>
+          <t>2026-08-26 22:08:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:49</t>
+          <t>2026-08-26 22:08:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:49</t>
+          <t>2026-08-26 22:08:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:49</t>
+          <t>2026-08-26 22:08:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:49</t>
+          <t>2026-08-26 22:08:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:49</t>
+          <t>2026-08-26 22:08:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:49</t>
+          <t>2026-08-26 22:08:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:49</t>
+          <t>2026-08-26 22:08:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:49</t>
+          <t>2026-08-26 22:08:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:49</t>
+          <t>2026-08-26 22:08:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:49</t>
+          <t>2026-08-26 22:08:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:50</t>
+          <t>2026-08-26 22:08:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:50</t>
+          <t>2026-08-26 22:08:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:50</t>
+          <t>2026-08-26 22:08:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:50</t>
+          <t>2026-08-26 22:08:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:50</t>
+          <t>2026-08-26 22:08:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:50</t>
+          <t>2026-08-26 22:08:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:50</t>
+          <t>2026-08-26 22:08:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:50</t>
+          <t>2026-08-26 22:08:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:50</t>
+          <t>2026-08-26 22:08:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:50</t>
+          <t>2026-08-26 22:08:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:50</t>
+          <t>2026-08-26 22:08:03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-26_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:01</t>
+          <t>2026-08-26 22:15:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:01</t>
+          <t>2026-08-26 22:15:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:01</t>
+          <t>2026-08-26 22:15:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:01</t>
+          <t>2026-08-26 22:15:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:01</t>
+          <t>2026-08-26 22:15:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:01</t>
+          <t>2026-08-26 22:15:23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:01</t>
+          <t>2026-08-26 22:15:23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:01</t>
+          <t>2026-08-26 22:15:23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:01</t>
+          <t>2026-08-26 22:15:23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:01</t>
+          <t>2026-08-26 22:15:23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:01</t>
+          <t>2026-08-26 22:15:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:01</t>
+          <t>2026-08-26 22:15:23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:01</t>
+          <t>2026-08-26 22:15:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:01</t>
+          <t>2026-08-26 22:15:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:01</t>
+          <t>2026-08-26 22:15:23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:02</t>
+          <t>2026-08-26 22:15:25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:02</t>
+          <t>2026-08-26 22:15:25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:02</t>
+          <t>2026-08-26 22:15:25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:02</t>
+          <t>2026-08-26 22:15:25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:02</t>
+          <t>2026-08-26 22:15:25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:02</t>
+          <t>2026-08-26 22:15:25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:02</t>
+          <t>2026-08-26 22:15:25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:02</t>
+          <t>2026-08-26 22:15:25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:02</t>
+          <t>2026-08-26 22:15:25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:02</t>
+          <t>2026-08-26 22:15:25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:02</t>
+          <t>2026-08-26 22:15:25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:02</t>
+          <t>2026-08-26 22:15:25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:02</t>
+          <t>2026-08-26 22:15:25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:02</t>
+          <t>2026-08-26 22:15:25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:02</t>
+          <t>2026-08-26 22:15:25</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:03</t>
+          <t>2026-08-26 22:15:26</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:03</t>
+          <t>2026-08-26 22:15:26</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:03</t>
+          <t>2026-08-26 22:15:26</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:03</t>
+          <t>2026-08-26 22:15:26</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:03</t>
+          <t>2026-08-26 22:15:26</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:03</t>
+          <t>2026-08-26 22:15:26</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:03</t>
+          <t>2026-08-26 22:15:26</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:03</t>
+          <t>2026-08-26 22:15:26</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:03</t>
+          <t>2026-08-26 22:15:26</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:03</t>
+          <t>2026-08-26 22:15:26</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 22:08:03</t>
+          <t>2026-08-26 22:15:26</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-26_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:23</t>
+          <t>2026-08-26 22:19:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:23</t>
+          <t>2026-08-26 22:19:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:23</t>
+          <t>2026-08-26 22:19:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:23</t>
+          <t>2026-08-26 22:19:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:23</t>
+          <t>2026-08-26 22:19:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:23</t>
+          <t>2026-08-26 22:19:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:23</t>
+          <t>2026-08-26 22:19:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:23</t>
+          <t>2026-08-26 22:19:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:23</t>
+          <t>2026-08-26 22:19:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:23</t>
+          <t>2026-08-26 22:19:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:23</t>
+          <t>2026-08-26 22:19:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:23</t>
+          <t>2026-08-26 22:19:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:23</t>
+          <t>2026-08-26 22:19:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:23</t>
+          <t>2026-08-26 22:19:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:23</t>
+          <t>2026-08-26 22:19:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:25</t>
+          <t>2026-08-26 22:19:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:25</t>
+          <t>2026-08-26 22:19:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:25</t>
+          <t>2026-08-26 22:19:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:25</t>
+          <t>2026-08-26 22:19:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:25</t>
+          <t>2026-08-26 22:19:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:25</t>
+          <t>2026-08-26 22:19:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:25</t>
+          <t>2026-08-26 22:19:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:25</t>
+          <t>2026-08-26 22:19:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:25</t>
+          <t>2026-08-26 22:19:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:25</t>
+          <t>2026-08-26 22:19:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:25</t>
+          <t>2026-08-26 22:19:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:25</t>
+          <t>2026-08-26 22:19:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:25</t>
+          <t>2026-08-26 22:19:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:25</t>
+          <t>2026-08-26 22:19:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:25</t>
+          <t>2026-08-26 22:19:47</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:26</t>
+          <t>2026-08-26 22:19:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:26</t>
+          <t>2026-08-26 22:19:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:26</t>
+          <t>2026-08-26 22:19:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:26</t>
+          <t>2026-08-26 22:19:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:26</t>
+          <t>2026-08-26 22:19:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:26</t>
+          <t>2026-08-26 22:19:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:26</t>
+          <t>2026-08-26 22:19:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:26</t>
+          <t>2026-08-26 22:19:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:26</t>
+          <t>2026-08-26 22:19:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:26</t>
+          <t>2026-08-26 22:19:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:26</t>
+          <t>2026-08-26 22:19:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
